--- a/Orçado/Orça-Agric/LAGUNA - GIRASSOL.xlsx
+++ b/Orçado/Orça-Agric/LAGUNA - GIRASSOL.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\henrique.santos\orcamento2027\budgetflow-insights\Orçado\Orça-Agric\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{558BE7A0-73CE-4ABB-B77D-EDF77C181C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{71380437-958B-4BAE-923D-DB7C7EC50163}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6964686B-2E82-465F-AF51-97AB90BAB5EF}"/>
+    <workbookView xWindow="-20520" yWindow="1920" windowWidth="20640" windowHeight="11040" xr2:uid="{1193E4E4-8D35-4517-8468-E41FAFFD768E}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,35 +41,64 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>GRUPO_CONTABIL</t>
   </si>
   <si>
-    <t>4.1.01.11-CUSTOS RURAIS</t>
+    <t>CONTA_CONTABIL</t>
   </si>
   <si>
-    <t>4.1.01.03-LOCACOES</t>
+    <t>Descrição C. Contábil</t>
   </si>
   <si>
-    <t>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</t>
+    <t>4.1.01.02.0004</t>
   </si>
   <si>
-    <t>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</t>
+    <t>4.1.01.11.0017</t>
   </si>
   <si>
-    <t>4.2.01.02-RATEIO DE CUSTOS</t>
+    <t>4.1.01.11.0019</t>
   </si>
   <si>
-    <t>4.1.01.02-SERVICOS DE TERCEIROS</t>
+    <t>4.2.01.02.0001</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -89,19 +121,38 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom/>
       <diagonal/>
     </border>
@@ -121,19 +172,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="17" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="17" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{91D4B136-CF17-4557-BF32-D5AC31449AAE}"/>
+    <cellStyle name="Normal 3" xfId="2" xr:uid="{24471426-CAF6-4CEC-855B-6C4EE94EC1FF}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -146,6 +205,281 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Planilha1"/>
+      <sheetName val="Planilha2"/>
+      <sheetName val="Planilha3"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2">
+        <row r="2">
+          <cell r="F2" t="str">
+            <v>4.1.01.02-SERVICOS DE TERCEIROS</v>
+          </cell>
+          <cell r="G2" t="str">
+            <v>4.1.01.02.0004</v>
+          </cell>
+          <cell r="H2" t="str">
+            <v>FRETES E CARRETOS PJ</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="F3" t="str">
+            <v>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</v>
+          </cell>
+          <cell r="G3" t="str">
+            <v>4.1.01.04.0001</v>
+          </cell>
+          <cell r="H3" t="str">
+            <v>COMBUSTIVEIS E LUBRIFICANTES</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="F4" t="str">
+            <v>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</v>
+          </cell>
+          <cell r="G4" t="str">
+            <v>4.1.01.04.0002</v>
+          </cell>
+          <cell r="H4" t="str">
+            <v>COMBUSTIVEIS E LUBRIFICANTES</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="F5" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G5" t="str">
+            <v>4.1.01.11.0017</v>
+          </cell>
+          <cell r="H5" t="str">
+            <v>FERTILIZANTES</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="F6" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G6" t="str">
+            <v>4.1.01.11.0019</v>
+          </cell>
+          <cell r="H6" t="str">
+            <v>HERBICIDAS E DEFENSIVOS</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="F7" t="str">
+            <v>4.2.01.02-RATEIO DE CUSTOS</v>
+          </cell>
+          <cell r="G7" t="str">
+            <v>4.2.01.02.0001</v>
+          </cell>
+          <cell r="H7" t="str">
+            <v>RATEIO RECEBIDO</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="F8" t="str">
+            <v>4.1.01.02-SERVICOS DE TERCEIROS</v>
+          </cell>
+          <cell r="G8" t="str">
+            <v>4.1.01.02.0002</v>
+          </cell>
+          <cell r="H8" t="str">
+            <v>SERVICOS DE TERCEIROS PJ</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="F9" t="str">
+            <v>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</v>
+          </cell>
+          <cell r="G9" t="str">
+            <v>4.1.01.04.0002</v>
+          </cell>
+          <cell r="H9" t="str">
+            <v>PECAS, ACESSORIOS E MATERIAIS</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="F10" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G10" t="str">
+            <v>4.1.01.11.0015</v>
+          </cell>
+          <cell r="H10" t="str">
+            <v xml:space="preserve">SEMENTES E MUDAS </v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="F11" t="str">
+            <v>4.1.01.03-LOCACOES</v>
+          </cell>
+          <cell r="G11" t="str">
+            <v>4.1.01.03.0010</v>
+          </cell>
+          <cell r="H11" t="str">
+            <v>LOCACOES DE MAQUINAS E EQUIPAMENTOS</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="F12" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G12" t="str">
+            <v>4.1.01.11.0015</v>
+          </cell>
+          <cell r="H12" t="str">
+            <v>SEMENTES E MUDAS</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="F13" t="str">
+            <v>4.1.01.02-SERVICOS DE TERCEIROS</v>
+          </cell>
+          <cell r="G13" t="str">
+            <v>4.1.01.02.0002</v>
+          </cell>
+          <cell r="H13" t="str">
+            <v>FRETES E CARRETOS PJ</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="F14" t="str">
+            <v>4.1.01.04-MANUTENCAO E CONSERVACAO DE BENS</v>
+          </cell>
+          <cell r="G14" t="str">
+            <v>4.1.01.04.0005</v>
+          </cell>
+          <cell r="H14" t="str">
+            <v>MATERIAIS DE CONSERVACAO E LIMPEZA</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="F15" t="str">
+            <v>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+          <cell r="G15" t="str">
+            <v>4.1.01.21.0002</v>
+          </cell>
+          <cell r="H15" t="str">
+            <v>TAXAS E ANUIDADES</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="F16" t="str">
+            <v>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+          <cell r="G16" t="str">
+            <v>4.1.01.21.0002</v>
+          </cell>
+          <cell r="H16" t="str">
+            <v>EQUIPAMENTOS DE SEGURANCA NO TRABALHO</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="F17" t="str">
+            <v>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+          <cell r="G17" t="str">
+            <v>4.1.01.21.0012</v>
+          </cell>
+          <cell r="H17" t="str">
+            <v>LANCHES E REFEICOES</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="F18" t="str">
+            <v>4.1.01.02-SERVICOS DE TERCEIROS</v>
+          </cell>
+          <cell r="G18" t="str">
+            <v>4.1.01.02.0004</v>
+          </cell>
+          <cell r="H18" t="str">
+            <v>SERVIÇOS DE TERCEIROS PJ</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="F19" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G19" t="str">
+            <v>4.1.01.11.0017</v>
+          </cell>
+          <cell r="H19" t="str">
+            <v>HERBICIDAS E DEFENSIVOS</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="F20" t="str">
+            <v>4.1.01.03-LOCACOES</v>
+          </cell>
+          <cell r="G20" t="str">
+            <v>4.1.01.03.0006</v>
+          </cell>
+          <cell r="H20" t="str">
+            <v>LOCACOES DE AREAS AGRICOLAS</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="F21" t="str">
+            <v>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+          <cell r="G21" t="str">
+            <v>4.1.01.21.0002</v>
+          </cell>
+          <cell r="H21" t="str">
+            <v>LANCHES E REFEICOES</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="F22" t="str">
+            <v>4.1.01.11-CUSTOS RURAIS</v>
+          </cell>
+          <cell r="G22" t="str">
+            <v>4.1.01.11.0019</v>
+          </cell>
+          <cell r="H22" t="str">
+            <v>SEMENTES E MUDAS</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="F23" t="str">
+            <v>4.1.01.05-DEPRECIACOES, EXAUSTOES E AMORTIZACOES</v>
+          </cell>
+          <cell r="G23" t="str">
+            <v>4.1.01.05.0001</v>
+          </cell>
+          <cell r="H23" t="str">
+            <v>DEPRECIACOES</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="F24" t="str">
+            <v>4.1.01.21-OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+          <cell r="G24" t="str">
+            <v>4.1.01.21.0020</v>
+          </cell>
+          <cell r="H24" t="str">
+            <v>OUTROS CUSTOS OPERACIONAIS</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,381 +798,177 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0344BA3A-9134-4FFE-9D3A-94AD89917517}">
-  <dimension ref="A1:M9"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01000A2C-729F-43C4-AB14-B841C9E135C3}">
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="48.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="13" width="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="44.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="35.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="14" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
         <v>46113</v>
       </c>
-      <c r="C1" s="2">
+      <c r="E1" s="3">
         <v>46143</v>
       </c>
-      <c r="D1" s="2">
+      <c r="F1" s="3">
         <v>46174</v>
       </c>
-      <c r="E1" s="2">
+      <c r="G1" s="3">
         <v>46204</v>
       </c>
-      <c r="F1" s="2">
+      <c r="H1" s="3">
         <v>46235</v>
       </c>
-      <c r="G1" s="2">
+      <c r="I1" s="3">
         <v>46266</v>
       </c>
-      <c r="H1" s="2">
+      <c r="J1" s="3">
         <v>46296</v>
       </c>
-      <c r="I1" s="2">
+      <c r="K1" s="3">
         <v>46327</v>
       </c>
-      <c r="J1" s="2">
+      <c r="L1" s="3">
         <v>46357</v>
       </c>
-      <c r="K1" s="2">
+      <c r="M1" s="3">
         <v>46388</v>
       </c>
-      <c r="L1" s="2">
+      <c r="N1" s="3">
         <v>46419</v>
       </c>
-      <c r="M1" s="2">
+      <c r="O1" s="3">
         <v>46447</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A2" t="str" cm="1">
+        <f t="array" ref="A2:A5">_xlfn.XLOOKUP(B2:B5,[1]Planilha3!$G$2:$G$24,[1]Planilha3!$F$2:$F$24,"")</f>
+        <v>4.1.01.02-SERVICOS DE TERCEIROS</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="str" cm="1">
+        <f t="array" ref="C2:C5">_xlfn.XLOOKUP(B2:B5,[1]Planilha3!$G$2:$G$24,[1]Planilha3!$H$2:$H$24,"")</f>
+        <v>FRETES E CARRETOS PJ</v>
+      </c>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5">
+        <v>15224.999999999998</v>
+      </c>
+      <c r="H2" s="5"/>
+      <c r="I2" s="5"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="5"/>
+      <c r="L2" s="5"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A3" t="str">
+        <v>4.1.01.11-CUSTOS RURAIS</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" t="str">
+        <v>FERTILIZANTES</v>
+      </c>
+      <c r="D3" s="5"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5"/>
+      <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5">
+        <v>40680</v>
+      </c>
+      <c r="O3" s="5">
         <v>0</v>
       </c>
-      <c r="C2" s="3">
-        <v>0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0</v>
-      </c>
-      <c r="F2" s="3">
-        <v>0</v>
-      </c>
-      <c r="G2" s="3">
-        <v>0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0</v>
-      </c>
-      <c r="I2" s="3">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3">
-        <v>0</v>
-      </c>
-      <c r="K2" s="3">
-        <v>0</v>
-      </c>
-      <c r="L2" s="3">
-        <v>40680</v>
-      </c>
-      <c r="M2" s="3">
-        <v>0</v>
-      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0</v>
-      </c>
-      <c r="I3" s="3">
-        <v>0</v>
-      </c>
-      <c r="J3" s="3">
-        <v>0</v>
-      </c>
-      <c r="K3" s="3">
-        <v>0</v>
-      </c>
-      <c r="L3" s="3">
-        <v>15909.5</v>
-      </c>
-      <c r="M3" s="3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A4" t="str">
+        <v>4.1.01.11-CUSTOS RURAIS</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="str">
+        <v>HERBICIDAS E DEFENSIVOS</v>
+      </c>
+      <c r="D4" s="5"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5">
+        <v>30037.5</v>
+      </c>
+      <c r="O4" s="5">
         <v>13481.9</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0</v>
-      </c>
-      <c r="I4" s="3">
-        <v>0</v>
-      </c>
-      <c r="J4" s="3">
-        <v>0</v>
-      </c>
-      <c r="K4" s="3">
-        <v>0</v>
-      </c>
-      <c r="L4" s="3">
-        <v>0</v>
-      </c>
-      <c r="M4" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0</v>
-      </c>
-      <c r="I5" s="3">
-        <v>0</v>
-      </c>
-      <c r="J5" s="3">
-        <v>0</v>
-      </c>
-      <c r="K5" s="3">
-        <v>0</v>
-      </c>
-      <c r="L5" s="3">
-        <v>0</v>
-      </c>
-      <c r="M5" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0</v>
-      </c>
-      <c r="H6" s="3">
-        <v>0</v>
-      </c>
-      <c r="I6" s="3">
-        <v>0</v>
-      </c>
-      <c r="J6" s="3">
-        <v>0</v>
-      </c>
-      <c r="K6" s="3">
-        <v>0</v>
-      </c>
-      <c r="L6" s="3">
-        <v>0</v>
-      </c>
-      <c r="M6" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A5" t="str">
+        <v>4.2.01.02-RATEIO DE CUSTOS</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C5" t="str">
+        <v>RATEIO RECEBIDO</v>
+      </c>
+      <c r="D5" s="5">
         <v>3000</v>
       </c>
-      <c r="C7" s="3">
-        <v>0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5">
         <v>17500</v>
       </c>
-      <c r="F7" s="3">
-        <v>0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0</v>
-      </c>
-      <c r="I7" s="3">
-        <v>0</v>
-      </c>
-      <c r="J7" s="3">
-        <v>0</v>
-      </c>
-      <c r="K7" s="3">
-        <v>0</v>
-      </c>
-      <c r="L7" s="3">
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
+      <c r="K5" s="5"/>
+      <c r="L5" s="5"/>
+      <c r="M5" s="5"/>
+      <c r="N5" s="5">
         <v>21245.75</v>
       </c>
-      <c r="M7" s="3">
+      <c r="O5" s="5">
         <v>3000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0</v>
-      </c>
-      <c r="D8" s="3">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3">
-        <v>0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0</v>
-      </c>
-      <c r="I8" s="3">
-        <v>0</v>
-      </c>
-      <c r="J8" s="3">
-        <v>0</v>
-      </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3">
-        <v>14128</v>
-      </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>0</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>15224.999999999998</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>0</v>
-      </c>
-      <c r="I9" s="3">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3">
-        <v>0</v>
-      </c>
-      <c r="K9" s="3">
-        <v>0</v>
-      </c>
-      <c r="L9" s="3">
-        <v>0</v>
-      </c>
-      <c r="M9" s="3">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
